--- a/uploads/Enfoque_Diario_DOMINGO_SGH_2026.xlsx
+++ b/uploads/Enfoque_Diario_DOMINGO_SGH_2026.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="6" activeTab="10" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DOMINGO" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLAN.ACCIÓN_D" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LUNES" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLAN.ACCIÓN_L" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MARTES" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLAN.ACCIÓN_MA" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MIÉRCOLES" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLAN.ACCIÓN_MI" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="JUEVES" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLAN.ACCIÓN_J" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIERNES" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLAN.ACCIÓN_V" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SÁBADO" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLAN.ACCIÓN_S" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SEMANAL" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="DOMINGO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="PLAN.ACCIÓN_D" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="LUNES" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="PLAN.ACCIÓN_L" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="MARTES" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="PLAN.ACCIÓN_MA" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="MIÉRCOLES" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PLAN.ACCIÓN_MI" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="JUEVES" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="PLAN.ACCIÓN_J" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="VIERNES" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="PLAN.ACCIÓN_V" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="SÁBADO" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="PLAN.ACCIÓN_S" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="SEMANAL" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'DOMINGO'!$A$1:$Q$41</definedName>
@@ -32060,7 +32060,7 @@
         </is>
       </c>
       <c r="K1" s="118" t="n">
-        <v>46244.341169226</v>
+        <v>46248.18697223458</v>
       </c>
       <c r="L1" s="19" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
       </c>
       <c r="M1" s="134" t="inlineStr">
         <is>
-          <t>Interlomas</t>
+          <t>Vallejo</t>
         </is>
       </c>
       <c r="N1" s="118" t="n"/>
@@ -32156,7 +32156,7 @@
         </is>
       </c>
       <c r="C5" s="93" t="n">
-        <v>6000</v>
+        <v>3620</v>
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
@@ -32164,7 +32164,7 @@
         </is>
       </c>
       <c r="F5" s="96" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
@@ -32205,7 +32205,7 @@
         </is>
       </c>
       <c r="F6" s="97" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
@@ -32267,7 +32267,7 @@
         <v/>
       </c>
       <c r="P7" s="240" t="n">
-        <v>5000</v>
+        <v>3620</v>
       </c>
       <c r="Q7" s="27" t="n"/>
     </row>
@@ -32312,7 +32312,7 @@
     </row>
     <row r="9" ht="46.05" customHeight="1" thickBot="1">
       <c r="E9" s="172" t="n">
-        <v>4800</v>
+        <v>3620</v>
       </c>
       <c r="F9" s="241" t="n"/>
       <c r="J9" s="30" t="n"/>
@@ -32325,7 +32325,7 @@
         <v>4758</v>
       </c>
       <c r="P9" s="242" t="n">
-        <v>5000</v>
+        <v>3620</v>
       </c>
       <c r="Q9" s="27" t="n"/>
     </row>
@@ -32382,19 +32382,19 @@
         </is>
       </c>
       <c r="C12" s="165" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12" s="166" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12" s="166" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F12" s="166" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G12" s="85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" s="86">
         <f>SUM(C12:G12)</f>
@@ -32437,7 +32437,7 @@
       <c r="H13" s="89" t="n"/>
       <c r="N13" s="169" t="n"/>
       <c r="P13" s="240" t="n">
-        <v>5000</v>
+        <v>7597</v>
       </c>
       <c r="Q13" s="27" t="n"/>
     </row>
@@ -32490,7 +32490,7 @@
       <c r="K15" s="28" t="n"/>
       <c r="L15" s="28" t="n"/>
       <c r="P15" s="242" t="n">
-        <v>5000</v>
+        <v>3362</v>
       </c>
       <c r="Q15" s="27" t="n"/>
     </row>
@@ -32557,7 +32557,7 @@
       </c>
       <c r="C17" s="244" t="n"/>
       <c r="D17" s="132" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E17" s="72">
         <f>($C$5/$D$25)*D17</f>
@@ -32585,12 +32585,12 @@
       <c r="A18" s="33" t="n"/>
       <c r="B18" s="167" t="inlineStr">
         <is>
-          <t>romo</t>
+          <t>idalia</t>
         </is>
       </c>
       <c r="C18" s="245" t="n"/>
       <c r="D18" s="71" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" s="76">
         <f>($C$5/$D$25)*D18</f>
@@ -32601,9 +32601,8 @@
         <v/>
       </c>
       <c r="G18" s="124" t="n"/>
-      <c r="H18" s="78">
-        <f>IF(D18&gt;0,MAX(($J$6/$D$25)*D18,1),0)</f>
-        <v/>
+      <c r="H18" s="78" t="n">
+        <v>1</v>
       </c>
       <c r="I18" s="79">
         <f>IF(D18&gt;0,MAX(($J$7/$D$25)*D18,1),0)</f>
@@ -32618,12 +32617,12 @@
       <c r="A19" s="33" t="n"/>
       <c r="B19" s="167" t="inlineStr">
         <is>
-          <t>susana</t>
+          <t>viviana</t>
         </is>
       </c>
       <c r="C19" s="245" t="n"/>
       <c r="D19" s="71" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E19" s="76">
         <f>($C$5/$D$25)*D19</f>
@@ -32634,9 +32633,8 @@
         <v/>
       </c>
       <c r="G19" s="124" t="n"/>
-      <c r="H19" s="78">
-        <f>IF(D19&gt;0,MAX(($J$6/$D$25)*D19,1),0)</f>
-        <v/>
+      <c r="H19" s="78" t="n">
+        <v>1</v>
       </c>
       <c r="I19" s="79">
         <f>IF(D19&gt;0,MAX(($J$7/$D$25)*D19,1),0)</f>
@@ -32649,14 +32647,10 @@
     </row>
     <row r="20" ht="46.05" customFormat="1" customHeight="1" s="26">
       <c r="A20" s="33" t="n"/>
-      <c r="B20" s="167" t="inlineStr">
-        <is>
-          <t>pedro</t>
-        </is>
-      </c>
+      <c r="B20" s="167" t="inlineStr"/>
       <c r="C20" s="245" t="n"/>
       <c r="D20" s="71" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E20" s="76">
         <f>($C$5/$D$25)*D20</f>
@@ -32935,14 +32929,14 @@
         <v/>
       </c>
       <c r="E30" s="116" t="n">
-        <v>25600</v>
+        <v>0</v>
       </c>
       <c r="F30" s="115">
         <f>+C8</f>
         <v/>
       </c>
       <c r="G30" s="116" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H30" s="248">
         <f>G41/E41</f>
@@ -33062,11 +33056,11 @@
         <v/>
       </c>
       <c r="E33" s="160" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F33" s="256" t="n"/>
       <c r="G33" s="156" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H33" s="257" t="n"/>
       <c r="I33" s="122">
@@ -33074,26 +33068,26 @@
         <v/>
       </c>
       <c r="J33" s="110" t="n">
-        <v>13456</v>
+        <v>0</v>
       </c>
       <c r="K33" s="110" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L33" s="110" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M33" s="120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N33" s="122">
         <f>IFERROR(M33/L33,"0")</f>
         <v/>
       </c>
       <c r="O33" s="110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P33" s="111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q33" s="37" t="n"/>
     </row>
@@ -33109,11 +33103,11 @@
         <v/>
       </c>
       <c r="E34" s="147" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F34" s="260" t="n"/>
       <c r="G34" s="148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" s="261" t="n"/>
       <c r="I34" s="122">
@@ -33121,13 +33115,13 @@
         <v/>
       </c>
       <c r="J34" s="113" t="n">
-        <v>9344</v>
+        <v>0</v>
       </c>
       <c r="K34" s="113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M34" s="121" t="n">
         <v>0</v>
@@ -33156,11 +33150,11 @@
         <v/>
       </c>
       <c r="E35" s="147" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F35" s="260" t="n"/>
       <c r="G35" s="148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" s="261" t="n"/>
       <c r="I35" s="122">
@@ -33168,10 +33162,10 @@
         <v/>
       </c>
       <c r="J35" s="113" t="n">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="K35" s="113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" s="113" t="n">
         <v>0</v>
@@ -33214,16 +33208,28 @@
         <f>IFERROR(G36/E36,"0")</f>
         <v/>
       </c>
-      <c r="J36" s="113" t="n"/>
-      <c r="K36" s="113" t="n"/>
-      <c r="L36" s="113" t="n"/>
-      <c r="M36" s="121" t="n"/>
+      <c r="J36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N36" s="122">
         <f>IFERROR(M36/L36,"0")</f>
         <v/>
       </c>
-      <c r="O36" s="113" t="n"/>
-      <c r="P36" s="114" t="n"/>
+      <c r="O36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q36" s="37" t="n"/>
     </row>
     <row r="37" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -33237,24 +33243,40 @@
         <f>D21</f>
         <v/>
       </c>
-      <c r="E37" s="147" t="n"/>
+      <c r="E37" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F37" s="260" t="n"/>
-      <c r="G37" s="148" t="n"/>
+      <c r="G37" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H37" s="261" t="n"/>
       <c r="I37" s="122">
         <f>IFERROR(G37/E37,"0")</f>
         <v/>
       </c>
-      <c r="J37" s="113" t="n"/>
-      <c r="K37" s="113" t="n"/>
-      <c r="L37" s="113" t="n"/>
-      <c r="M37" s="121" t="n"/>
+      <c r="J37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N37" s="122">
         <f>IFERROR(M37/L37,"0")</f>
         <v/>
       </c>
-      <c r="O37" s="113" t="n"/>
-      <c r="P37" s="114" t="n"/>
+      <c r="O37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q37" s="37" t="n"/>
     </row>
     <row r="38" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -33268,24 +33290,40 @@
         <f>D22</f>
         <v/>
       </c>
-      <c r="E38" s="147" t="n"/>
+      <c r="E38" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F38" s="260" t="n"/>
-      <c r="G38" s="148" t="n"/>
+      <c r="G38" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H38" s="261" t="n"/>
       <c r="I38" s="122">
         <f>IFERROR(G38/E38,"0")</f>
         <v/>
       </c>
-      <c r="J38" s="113" t="n"/>
-      <c r="K38" s="113" t="n"/>
-      <c r="L38" s="113" t="n"/>
-      <c r="M38" s="121" t="n"/>
+      <c r="J38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N38" s="122">
         <f>IFERROR(M38/L38,"0")</f>
         <v/>
       </c>
-      <c r="O38" s="113" t="n"/>
-      <c r="P38" s="114" t="n"/>
+      <c r="O38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q38" s="37" t="n"/>
     </row>
     <row r="39" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -33299,24 +33337,40 @@
         <f>D23</f>
         <v/>
       </c>
-      <c r="E39" s="147" t="n"/>
+      <c r="E39" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F39" s="260" t="n"/>
-      <c r="G39" s="148" t="n"/>
+      <c r="G39" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H39" s="261" t="n"/>
       <c r="I39" s="122">
         <f>IFERROR(G39/E39,"0")</f>
         <v/>
       </c>
-      <c r="J39" s="113" t="n"/>
-      <c r="K39" s="113" t="n"/>
-      <c r="L39" s="113" t="n"/>
-      <c r="M39" s="121" t="n"/>
+      <c r="J39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N39" s="122">
         <f>IFERROR(M39/L39,"0")</f>
         <v/>
       </c>
-      <c r="O39" s="113" t="n"/>
-      <c r="P39" s="114" t="n"/>
+      <c r="O39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q39" s="37" t="n"/>
     </row>
     <row r="40" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -33330,24 +33384,40 @@
         <f>D24</f>
         <v/>
       </c>
-      <c r="E40" s="147" t="n"/>
+      <c r="E40" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F40" s="260" t="n"/>
-      <c r="G40" s="148" t="n"/>
+      <c r="G40" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H40" s="261" t="n"/>
       <c r="I40" s="122">
         <f>IFERROR(G40/E40,"0")</f>
         <v/>
       </c>
-      <c r="J40" s="113" t="n"/>
-      <c r="K40" s="113" t="n"/>
-      <c r="L40" s="113" t="n"/>
-      <c r="M40" s="121" t="n"/>
+      <c r="J40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N40" s="122">
         <f>IFERROR(M40/L40,"0")</f>
         <v/>
       </c>
-      <c r="O40" s="113" t="n"/>
-      <c r="P40" s="114" t="n"/>
+      <c r="O40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q40" s="37" t="n"/>
     </row>
     <row r="41" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -34157,7 +34227,7 @@
         </is>
       </c>
       <c r="K1" s="118" t="n">
-        <v>46244.34116926072</v>
+        <v>46248.18697224488</v>
       </c>
       <c r="L1" s="19" t="inlineStr">
         <is>
@@ -34166,7 +34236,7 @@
       </c>
       <c r="M1" s="134" t="inlineStr">
         <is>
-          <t>Interlomas</t>
+          <t>Vallejo</t>
         </is>
       </c>
       <c r="N1" s="118" t="n"/>
@@ -34682,7 +34752,7 @@
       <c r="A18" s="33" t="n"/>
       <c r="B18" s="167" t="inlineStr">
         <is>
-          <t>romo</t>
+          <t>idalia</t>
         </is>
       </c>
       <c r="C18" s="245" t="n"/>
@@ -34715,7 +34785,7 @@
       <c r="A19" s="33" t="n"/>
       <c r="B19" s="167" t="inlineStr">
         <is>
-          <t>susana</t>
+          <t>viviana</t>
         </is>
       </c>
       <c r="C19" s="245" t="n"/>
@@ -34746,14 +34816,10 @@
     </row>
     <row r="20" ht="46.05" customFormat="1" customHeight="1" s="26">
       <c r="A20" s="33" t="n"/>
-      <c r="B20" s="167" t="inlineStr">
-        <is>
-          <t>pedro</t>
-        </is>
-      </c>
+      <c r="B20" s="167" t="inlineStr"/>
       <c r="C20" s="245" t="n"/>
       <c r="D20" s="71" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E20" s="76">
         <f>($C$5/$D$25)*D20</f>
@@ -35032,14 +35098,14 @@
         <v/>
       </c>
       <c r="E30" s="116" t="n">
-        <v>25600</v>
+        <v>0</v>
       </c>
       <c r="F30" s="115">
         <f>+C8</f>
         <v/>
       </c>
       <c r="G30" s="116" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H30" s="248">
         <f>G41/E41</f>
@@ -35158,24 +35224,40 @@
         <f>D17</f>
         <v/>
       </c>
-      <c r="E33" s="160" t="n"/>
+      <c r="E33" s="160" t="n">
+        <v>0</v>
+      </c>
       <c r="F33" s="256" t="n"/>
-      <c r="G33" s="156" t="n"/>
+      <c r="G33" s="156" t="n">
+        <v>0</v>
+      </c>
       <c r="H33" s="257" t="n"/>
       <c r="I33" s="122">
         <f>IFERROR(G33/E33,"0")</f>
         <v/>
       </c>
-      <c r="J33" s="110" t="n"/>
-      <c r="K33" s="110" t="n"/>
-      <c r="L33" s="110" t="n"/>
-      <c r="M33" s="120" t="n"/>
+      <c r="J33" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="120" t="n">
+        <v>0</v>
+      </c>
       <c r="N33" s="122">
         <f>IFERROR(M33/L33,"0")</f>
         <v/>
       </c>
-      <c r="O33" s="110" t="n"/>
-      <c r="P33" s="111" t="n"/>
+      <c r="O33" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="111" t="n">
+        <v>0</v>
+      </c>
       <c r="Q33" s="37" t="n"/>
     </row>
     <row r="34" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -35189,24 +35271,40 @@
         <f>D18</f>
         <v/>
       </c>
-      <c r="E34" s="147" t="n"/>
+      <c r="E34" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F34" s="260" t="n"/>
-      <c r="G34" s="148" t="n"/>
+      <c r="G34" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H34" s="261" t="n"/>
       <c r="I34" s="122">
         <f>IFERROR(G34/E34,"0")</f>
         <v/>
       </c>
-      <c r="J34" s="113" t="n"/>
-      <c r="K34" s="113" t="n"/>
-      <c r="L34" s="113" t="n"/>
-      <c r="M34" s="121" t="n"/>
+      <c r="J34" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N34" s="122">
         <f>IFERROR(M34/L34,"0")</f>
         <v/>
       </c>
-      <c r="O34" s="113" t="n"/>
-      <c r="P34" s="114" t="n"/>
+      <c r="O34" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q34" s="37" t="n"/>
     </row>
     <row r="35" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -35220,24 +35318,40 @@
         <f>D19</f>
         <v/>
       </c>
-      <c r="E35" s="147" t="n"/>
+      <c r="E35" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F35" s="260" t="n"/>
-      <c r="G35" s="148" t="n"/>
+      <c r="G35" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H35" s="261" t="n"/>
       <c r="I35" s="122">
         <f>IFERROR(G35/E35,"0")</f>
         <v/>
       </c>
-      <c r="J35" s="113" t="n"/>
-      <c r="K35" s="113" t="n"/>
-      <c r="L35" s="113" t="n"/>
-      <c r="M35" s="121" t="n"/>
+      <c r="J35" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N35" s="122">
         <f>IFERROR(M35/L35,"0")</f>
         <v/>
       </c>
-      <c r="O35" s="113" t="n"/>
-      <c r="P35" s="114" t="n"/>
+      <c r="O35" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q35" s="37" t="n"/>
     </row>
     <row r="36" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -35251,24 +35365,40 @@
         <f>D20</f>
         <v/>
       </c>
-      <c r="E36" s="147" t="n"/>
+      <c r="E36" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F36" s="260" t="n"/>
-      <c r="G36" s="148" t="n"/>
+      <c r="G36" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H36" s="261" t="n"/>
       <c r="I36" s="122">
         <f>IFERROR(G36/E36,"0")</f>
         <v/>
       </c>
-      <c r="J36" s="113" t="n"/>
-      <c r="K36" s="113" t="n"/>
-      <c r="L36" s="113" t="n"/>
-      <c r="M36" s="121" t="n"/>
+      <c r="J36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N36" s="122">
         <f>IFERROR(M36/L36,"0")</f>
         <v/>
       </c>
-      <c r="O36" s="113" t="n"/>
-      <c r="P36" s="114" t="n"/>
+      <c r="O36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q36" s="37" t="n"/>
     </row>
     <row r="37" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -35282,24 +35412,40 @@
         <f>D21</f>
         <v/>
       </c>
-      <c r="E37" s="147" t="n"/>
+      <c r="E37" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F37" s="260" t="n"/>
-      <c r="G37" s="148" t="n"/>
+      <c r="G37" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H37" s="261" t="n"/>
       <c r="I37" s="122">
         <f>IFERROR(G37/E37,"0")</f>
         <v/>
       </c>
-      <c r="J37" s="113" t="n"/>
-      <c r="K37" s="113" t="n"/>
-      <c r="L37" s="113" t="n"/>
-      <c r="M37" s="121" t="n"/>
+      <c r="J37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N37" s="122">
         <f>IFERROR(M37/L37,"0")</f>
         <v/>
       </c>
-      <c r="O37" s="113" t="n"/>
-      <c r="P37" s="114" t="n"/>
+      <c r="O37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q37" s="37" t="n"/>
     </row>
     <row r="38" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -35313,24 +35459,40 @@
         <f>D22</f>
         <v/>
       </c>
-      <c r="E38" s="147" t="n"/>
+      <c r="E38" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F38" s="260" t="n"/>
-      <c r="G38" s="148" t="n"/>
+      <c r="G38" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H38" s="261" t="n"/>
       <c r="I38" s="122">
         <f>IFERROR(G38/E38,"0")</f>
         <v/>
       </c>
-      <c r="J38" s="113" t="n"/>
-      <c r="K38" s="113" t="n"/>
-      <c r="L38" s="113" t="n"/>
-      <c r="M38" s="121" t="n"/>
+      <c r="J38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N38" s="122">
         <f>IFERROR(M38/L38,"0")</f>
         <v/>
       </c>
-      <c r="O38" s="113" t="n"/>
-      <c r="P38" s="114" t="n"/>
+      <c r="O38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q38" s="37" t="n"/>
     </row>
     <row r="39" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -35344,24 +35506,40 @@
         <f>D23</f>
         <v/>
       </c>
-      <c r="E39" s="147" t="n"/>
+      <c r="E39" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F39" s="260" t="n"/>
-      <c r="G39" s="148" t="n"/>
+      <c r="G39" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H39" s="261" t="n"/>
       <c r="I39" s="122">
         <f>IFERROR(G39/E39,"0")</f>
         <v/>
       </c>
-      <c r="J39" s="113" t="n"/>
-      <c r="K39" s="113" t="n"/>
-      <c r="L39" s="113" t="n"/>
-      <c r="M39" s="121" t="n"/>
+      <c r="J39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N39" s="122">
         <f>IFERROR(M39/L39,"0")</f>
         <v/>
       </c>
-      <c r="O39" s="113" t="n"/>
-      <c r="P39" s="114" t="n"/>
+      <c r="O39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q39" s="37" t="n"/>
     </row>
     <row r="40" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -35375,24 +35553,40 @@
         <f>D24</f>
         <v/>
       </c>
-      <c r="E40" s="147" t="n"/>
+      <c r="E40" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F40" s="260" t="n"/>
-      <c r="G40" s="148" t="n"/>
+      <c r="G40" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H40" s="261" t="n"/>
       <c r="I40" s="122">
         <f>IFERROR(G40/E40,"0")</f>
         <v/>
       </c>
-      <c r="J40" s="113" t="n"/>
-      <c r="K40" s="113" t="n"/>
-      <c r="L40" s="113" t="n"/>
-      <c r="M40" s="121" t="n"/>
+      <c r="J40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N40" s="122">
         <f>IFERROR(M40/L40,"0")</f>
         <v/>
       </c>
-      <c r="O40" s="113" t="n"/>
-      <c r="P40" s="114" t="n"/>
+      <c r="O40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q40" s="37" t="n"/>
     </row>
     <row r="41" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -36219,7 +36413,7 @@
         </is>
       </c>
       <c r="K1" s="118" t="n">
-        <v>46244.34116926072</v>
+        <v>46248.18697224684</v>
       </c>
       <c r="L1" s="19" t="inlineStr">
         <is>
@@ -36228,7 +36422,7 @@
       </c>
       <c r="M1" s="134" t="inlineStr">
         <is>
-          <t>Interlomas</t>
+          <t>Vallejo</t>
         </is>
       </c>
       <c r="N1" s="118" t="n"/>
@@ -36742,7 +36936,7 @@
       <c r="A18" s="33" t="n"/>
       <c r="B18" s="167" t="inlineStr">
         <is>
-          <t>romo</t>
+          <t>idalia</t>
         </is>
       </c>
       <c r="C18" s="245" t="n"/>
@@ -36775,7 +36969,7 @@
       <c r="A19" s="33" t="n"/>
       <c r="B19" s="167" t="inlineStr">
         <is>
-          <t>susana</t>
+          <t>viviana</t>
         </is>
       </c>
       <c r="C19" s="245" t="n"/>
@@ -36806,14 +37000,10 @@
     </row>
     <row r="20" ht="46.05" customFormat="1" customHeight="1" s="26">
       <c r="A20" s="33" t="n"/>
-      <c r="B20" s="167" t="inlineStr">
-        <is>
-          <t>pedro</t>
-        </is>
-      </c>
+      <c r="B20" s="167" t="inlineStr"/>
       <c r="C20" s="245" t="n"/>
       <c r="D20" s="71" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E20" s="76">
         <f>($C$5/$D$25)*D20</f>
@@ -37092,14 +37282,14 @@
         <v/>
       </c>
       <c r="E30" s="116" t="n">
-        <v>25600</v>
+        <v>0</v>
       </c>
       <c r="F30" s="115">
         <f>+C8</f>
         <v/>
       </c>
       <c r="G30" s="116" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H30" s="248">
         <f>G41/E41</f>
@@ -37218,24 +37408,40 @@
         <f>D17</f>
         <v/>
       </c>
-      <c r="E33" s="160" t="n"/>
+      <c r="E33" s="160" t="n">
+        <v>0</v>
+      </c>
       <c r="F33" s="256" t="n"/>
-      <c r="G33" s="156" t="n"/>
+      <c r="G33" s="156" t="n">
+        <v>0</v>
+      </c>
       <c r="H33" s="257" t="n"/>
       <c r="I33" s="122">
         <f>IFERROR(G33/E33,"0")</f>
         <v/>
       </c>
-      <c r="J33" s="110" t="n"/>
-      <c r="K33" s="110" t="n"/>
-      <c r="L33" s="110" t="n"/>
-      <c r="M33" s="120" t="n"/>
+      <c r="J33" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="120" t="n">
+        <v>0</v>
+      </c>
       <c r="N33" s="122">
         <f>IFERROR(M33/L33,"0")</f>
         <v/>
       </c>
-      <c r="O33" s="110" t="n"/>
-      <c r="P33" s="111" t="n"/>
+      <c r="O33" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="111" t="n">
+        <v>0</v>
+      </c>
       <c r="Q33" s="37" t="n"/>
     </row>
     <row r="34" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -37249,24 +37455,40 @@
         <f>D18</f>
         <v/>
       </c>
-      <c r="E34" s="147" t="n"/>
+      <c r="E34" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F34" s="260" t="n"/>
-      <c r="G34" s="148" t="n"/>
+      <c r="G34" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H34" s="261" t="n"/>
       <c r="I34" s="122">
         <f>IFERROR(G34/E34,"0")</f>
         <v/>
       </c>
-      <c r="J34" s="113" t="n"/>
-      <c r="K34" s="113" t="n"/>
-      <c r="L34" s="113" t="n"/>
-      <c r="M34" s="121" t="n"/>
+      <c r="J34" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N34" s="122">
         <f>IFERROR(M34/L34,"0")</f>
         <v/>
       </c>
-      <c r="O34" s="113" t="n"/>
-      <c r="P34" s="114" t="n"/>
+      <c r="O34" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q34" s="37" t="n"/>
     </row>
     <row r="35" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -37280,24 +37502,40 @@
         <f>D19</f>
         <v/>
       </c>
-      <c r="E35" s="147" t="n"/>
+      <c r="E35" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F35" s="260" t="n"/>
-      <c r="G35" s="148" t="n"/>
+      <c r="G35" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H35" s="261" t="n"/>
       <c r="I35" s="122">
         <f>IFERROR(G35/E35,"0")</f>
         <v/>
       </c>
-      <c r="J35" s="113" t="n"/>
-      <c r="K35" s="113" t="n"/>
-      <c r="L35" s="113" t="n"/>
-      <c r="M35" s="121" t="n"/>
+      <c r="J35" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N35" s="122">
         <f>IFERROR(M35/L35,"0")</f>
         <v/>
       </c>
-      <c r="O35" s="113" t="n"/>
-      <c r="P35" s="114" t="n"/>
+      <c r="O35" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q35" s="37" t="n"/>
     </row>
     <row r="36" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -37311,24 +37549,40 @@
         <f>D20</f>
         <v/>
       </c>
-      <c r="E36" s="147" t="n"/>
+      <c r="E36" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F36" s="260" t="n"/>
-      <c r="G36" s="148" t="n"/>
+      <c r="G36" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H36" s="261" t="n"/>
       <c r="I36" s="122">
         <f>IFERROR(G36/E36,"0")</f>
         <v/>
       </c>
-      <c r="J36" s="113" t="n"/>
-      <c r="K36" s="113" t="n"/>
-      <c r="L36" s="113" t="n"/>
-      <c r="M36" s="121" t="n"/>
+      <c r="J36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N36" s="122">
         <f>IFERROR(M36/L36,"0")</f>
         <v/>
       </c>
-      <c r="O36" s="113" t="n"/>
-      <c r="P36" s="114" t="n"/>
+      <c r="O36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q36" s="37" t="n"/>
     </row>
     <row r="37" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -37342,24 +37596,40 @@
         <f>D21</f>
         <v/>
       </c>
-      <c r="E37" s="147" t="n"/>
+      <c r="E37" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F37" s="260" t="n"/>
-      <c r="G37" s="148" t="n"/>
+      <c r="G37" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H37" s="261" t="n"/>
       <c r="I37" s="122">
         <f>IFERROR(G37/E37,"0")</f>
         <v/>
       </c>
-      <c r="J37" s="113" t="n"/>
-      <c r="K37" s="113" t="n"/>
-      <c r="L37" s="113" t="n"/>
-      <c r="M37" s="121" t="n"/>
+      <c r="J37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N37" s="122">
         <f>IFERROR(M37/L37,"0")</f>
         <v/>
       </c>
-      <c r="O37" s="113" t="n"/>
-      <c r="P37" s="114" t="n"/>
+      <c r="O37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q37" s="37" t="n"/>
     </row>
     <row r="38" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -37373,24 +37643,40 @@
         <f>D22</f>
         <v/>
       </c>
-      <c r="E38" s="147" t="n"/>
+      <c r="E38" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F38" s="260" t="n"/>
-      <c r="G38" s="148" t="n"/>
+      <c r="G38" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H38" s="261" t="n"/>
       <c r="I38" s="122">
         <f>IFERROR(G38/E38,"0")</f>
         <v/>
       </c>
-      <c r="J38" s="113" t="n"/>
-      <c r="K38" s="113" t="n"/>
-      <c r="L38" s="113" t="n"/>
-      <c r="M38" s="121" t="n"/>
+      <c r="J38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N38" s="122">
         <f>IFERROR(M38/L38,"0")</f>
         <v/>
       </c>
-      <c r="O38" s="113" t="n"/>
-      <c r="P38" s="114" t="n"/>
+      <c r="O38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q38" s="37" t="n"/>
     </row>
     <row r="39" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -37404,24 +37690,40 @@
         <f>D23</f>
         <v/>
       </c>
-      <c r="E39" s="147" t="n"/>
+      <c r="E39" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F39" s="260" t="n"/>
-      <c r="G39" s="148" t="n"/>
+      <c r="G39" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H39" s="261" t="n"/>
       <c r="I39" s="122">
         <f>IFERROR(G39/E39,"0")</f>
         <v/>
       </c>
-      <c r="J39" s="113" t="n"/>
-      <c r="K39" s="113" t="n"/>
-      <c r="L39" s="113" t="n"/>
-      <c r="M39" s="121" t="n"/>
+      <c r="J39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N39" s="122">
         <f>IFERROR(M39/L39,"0")</f>
         <v/>
       </c>
-      <c r="O39" s="113" t="n"/>
-      <c r="P39" s="114" t="n"/>
+      <c r="O39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q39" s="37" t="n"/>
     </row>
     <row r="40" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -37435,24 +37737,40 @@
         <f>D24</f>
         <v/>
       </c>
-      <c r="E40" s="147" t="n"/>
+      <c r="E40" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F40" s="260" t="n"/>
-      <c r="G40" s="148" t="n"/>
+      <c r="G40" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H40" s="261" t="n"/>
       <c r="I40" s="122">
         <f>IFERROR(G40/E40,"0")</f>
         <v/>
       </c>
-      <c r="J40" s="113" t="n"/>
-      <c r="K40" s="113" t="n"/>
-      <c r="L40" s="113" t="n"/>
-      <c r="M40" s="121" t="n"/>
+      <c r="J40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N40" s="122">
         <f>IFERROR(M40/L40,"0")</f>
         <v/>
       </c>
-      <c r="O40" s="113" t="n"/>
-      <c r="P40" s="114" t="n"/>
+      <c r="O40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q40" s="37" t="n"/>
     </row>
     <row r="41" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -39929,7 +40247,7 @@
         </is>
       </c>
       <c r="K1" s="118" t="n">
-        <v>46244.34116923758</v>
+        <v>46248.18697223661</v>
       </c>
       <c r="L1" s="19" t="inlineStr">
         <is>
@@ -39938,7 +40256,7 @@
       </c>
       <c r="M1" s="134" t="inlineStr">
         <is>
-          <t>Interlomas</t>
+          <t>Vallejo</t>
         </is>
       </c>
       <c r="N1" s="118" t="n"/>
@@ -40452,7 +40770,7 @@
       <c r="A18" s="33" t="n"/>
       <c r="B18" s="167" t="inlineStr">
         <is>
-          <t>romo</t>
+          <t>idalia</t>
         </is>
       </c>
       <c r="C18" s="245" t="n"/>
@@ -40485,7 +40803,7 @@
       <c r="A19" s="33" t="n"/>
       <c r="B19" s="167" t="inlineStr">
         <is>
-          <t>susana</t>
+          <t>viviana</t>
         </is>
       </c>
       <c r="C19" s="245" t="n"/>
@@ -40516,14 +40834,10 @@
     </row>
     <row r="20" ht="46.05" customFormat="1" customHeight="1" s="26">
       <c r="A20" s="33" t="n"/>
-      <c r="B20" s="167" t="inlineStr">
-        <is>
-          <t>pedro</t>
-        </is>
-      </c>
+      <c r="B20" s="167" t="inlineStr"/>
       <c r="C20" s="245" t="n"/>
       <c r="D20" s="71" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E20" s="76">
         <f>($C$5/$D$25)*D20</f>
@@ -40802,14 +41116,14 @@
         <v/>
       </c>
       <c r="E30" s="116" t="n">
-        <v>25600</v>
+        <v>0</v>
       </c>
       <c r="F30" s="115">
         <f>+C8</f>
         <v/>
       </c>
       <c r="G30" s="116" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H30" s="248">
         <f>G41/E41</f>
@@ -40928,24 +41242,40 @@
         <f>D17</f>
         <v/>
       </c>
-      <c r="E33" s="160" t="n"/>
+      <c r="E33" s="160" t="n">
+        <v>0</v>
+      </c>
       <c r="F33" s="256" t="n"/>
-      <c r="G33" s="156" t="n"/>
+      <c r="G33" s="156" t="n">
+        <v>0</v>
+      </c>
       <c r="H33" s="257" t="n"/>
       <c r="I33" s="122">
         <f>IFERROR(G33/E33,"0")</f>
         <v/>
       </c>
-      <c r="J33" s="110" t="n"/>
-      <c r="K33" s="110" t="n"/>
-      <c r="L33" s="110" t="n"/>
-      <c r="M33" s="120" t="n"/>
+      <c r="J33" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="120" t="n">
+        <v>0</v>
+      </c>
       <c r="N33" s="122">
         <f>IFERROR(M33/L33,"0")</f>
         <v/>
       </c>
-      <c r="O33" s="110" t="n"/>
-      <c r="P33" s="111" t="n"/>
+      <c r="O33" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="111" t="n">
+        <v>0</v>
+      </c>
       <c r="Q33" s="37" t="n"/>
     </row>
     <row r="34" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -40959,24 +41289,40 @@
         <f>D18</f>
         <v/>
       </c>
-      <c r="E34" s="147" t="n"/>
+      <c r="E34" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F34" s="260" t="n"/>
-      <c r="G34" s="148" t="n"/>
+      <c r="G34" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H34" s="261" t="n"/>
       <c r="I34" s="122">
         <f>IFERROR(G34/E34,"0")</f>
         <v/>
       </c>
-      <c r="J34" s="113" t="n"/>
-      <c r="K34" s="113" t="n"/>
-      <c r="L34" s="113" t="n"/>
-      <c r="M34" s="121" t="n"/>
+      <c r="J34" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N34" s="122">
         <f>IFERROR(M34/L34,"0")</f>
         <v/>
       </c>
-      <c r="O34" s="113" t="n"/>
-      <c r="P34" s="114" t="n"/>
+      <c r="O34" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q34" s="37" t="n"/>
     </row>
     <row r="35" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -40990,24 +41336,40 @@
         <f>D19</f>
         <v/>
       </c>
-      <c r="E35" s="147" t="n"/>
+      <c r="E35" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F35" s="260" t="n"/>
-      <c r="G35" s="148" t="n"/>
+      <c r="G35" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H35" s="261" t="n"/>
       <c r="I35" s="122">
         <f>IFERROR(G35/E35,"0")</f>
         <v/>
       </c>
-      <c r="J35" s="113" t="n"/>
-      <c r="K35" s="113" t="n"/>
-      <c r="L35" s="113" t="n"/>
-      <c r="M35" s="121" t="n"/>
+      <c r="J35" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N35" s="122">
         <f>IFERROR(M35/L35,"0")</f>
         <v/>
       </c>
-      <c r="O35" s="113" t="n"/>
-      <c r="P35" s="114" t="n"/>
+      <c r="O35" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q35" s="37" t="n"/>
     </row>
     <row r="36" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -41021,24 +41383,40 @@
         <f>D20</f>
         <v/>
       </c>
-      <c r="E36" s="147" t="n"/>
+      <c r="E36" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F36" s="260" t="n"/>
-      <c r="G36" s="148" t="n"/>
+      <c r="G36" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H36" s="261" t="n"/>
       <c r="I36" s="122">
         <f>IFERROR(G36/E36,"0")</f>
         <v/>
       </c>
-      <c r="J36" s="113" t="n"/>
-      <c r="K36" s="113" t="n"/>
-      <c r="L36" s="113" t="n"/>
-      <c r="M36" s="121" t="n"/>
+      <c r="J36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N36" s="122">
         <f>IFERROR(M36/L36,"0")</f>
         <v/>
       </c>
-      <c r="O36" s="113" t="n"/>
-      <c r="P36" s="114" t="n"/>
+      <c r="O36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q36" s="37" t="n"/>
     </row>
     <row r="37" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -41052,24 +41430,40 @@
         <f>D21</f>
         <v/>
       </c>
-      <c r="E37" s="147" t="n"/>
+      <c r="E37" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F37" s="260" t="n"/>
-      <c r="G37" s="148" t="n"/>
+      <c r="G37" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H37" s="261" t="n"/>
       <c r="I37" s="122">
         <f>IFERROR(G37/E37,"0")</f>
         <v/>
       </c>
-      <c r="J37" s="113" t="n"/>
-      <c r="K37" s="113" t="n"/>
-      <c r="L37" s="113" t="n"/>
-      <c r="M37" s="121" t="n"/>
+      <c r="J37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N37" s="122">
         <f>IFERROR(M37/L37,"0")</f>
         <v/>
       </c>
-      <c r="O37" s="113" t="n"/>
-      <c r="P37" s="114" t="n"/>
+      <c r="O37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q37" s="37" t="n"/>
     </row>
     <row r="38" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -41083,24 +41477,40 @@
         <f>D22</f>
         <v/>
       </c>
-      <c r="E38" s="147" t="n"/>
+      <c r="E38" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F38" s="260" t="n"/>
-      <c r="G38" s="148" t="n"/>
+      <c r="G38" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H38" s="261" t="n"/>
       <c r="I38" s="122">
         <f>IFERROR(G38/E38,"0")</f>
         <v/>
       </c>
-      <c r="J38" s="113" t="n"/>
-      <c r="K38" s="113" t="n"/>
-      <c r="L38" s="113" t="n"/>
-      <c r="M38" s="121" t="n"/>
+      <c r="J38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N38" s="122">
         <f>IFERROR(M38/L38,"0")</f>
         <v/>
       </c>
-      <c r="O38" s="113" t="n"/>
-      <c r="P38" s="114" t="n"/>
+      <c r="O38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q38" s="37" t="n"/>
     </row>
     <row r="39" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -41114,24 +41524,40 @@
         <f>D23</f>
         <v/>
       </c>
-      <c r="E39" s="147" t="n"/>
+      <c r="E39" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F39" s="260" t="n"/>
-      <c r="G39" s="148" t="n"/>
+      <c r="G39" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H39" s="261" t="n"/>
       <c r="I39" s="122">
         <f>IFERROR(G39/E39,"0")</f>
         <v/>
       </c>
-      <c r="J39" s="113" t="n"/>
-      <c r="K39" s="113" t="n"/>
-      <c r="L39" s="113" t="n"/>
-      <c r="M39" s="121" t="n"/>
+      <c r="J39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N39" s="122">
         <f>IFERROR(M39/L39,"0")</f>
         <v/>
       </c>
-      <c r="O39" s="113" t="n"/>
-      <c r="P39" s="114" t="n"/>
+      <c r="O39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q39" s="37" t="n"/>
     </row>
     <row r="40" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -41145,24 +41571,40 @@
         <f>D24</f>
         <v/>
       </c>
-      <c r="E40" s="147" t="n"/>
+      <c r="E40" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F40" s="260" t="n"/>
-      <c r="G40" s="148" t="n"/>
+      <c r="G40" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H40" s="261" t="n"/>
       <c r="I40" s="122">
         <f>IFERROR(G40/E40,"0")</f>
         <v/>
       </c>
-      <c r="J40" s="113" t="n"/>
-      <c r="K40" s="113" t="n"/>
-      <c r="L40" s="113" t="n"/>
-      <c r="M40" s="121" t="n"/>
+      <c r="J40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N40" s="122">
         <f>IFERROR(M40/L40,"0")</f>
         <v/>
       </c>
-      <c r="O40" s="113" t="n"/>
-      <c r="P40" s="114" t="n"/>
+      <c r="O40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q40" s="37" t="n"/>
     </row>
     <row r="41" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -41983,7 +42425,7 @@
         </is>
       </c>
       <c r="K1" s="118" t="n">
-        <v>46244.34116923758</v>
+        <v>46248.18697223869</v>
       </c>
       <c r="L1" s="19" t="inlineStr">
         <is>
@@ -41992,7 +42434,7 @@
       </c>
       <c r="M1" s="134" t="inlineStr">
         <is>
-          <t>Interlomas</t>
+          <t>Vallejo</t>
         </is>
       </c>
       <c r="N1" s="118" t="n"/>
@@ -42506,7 +42948,7 @@
       <c r="A18" s="33" t="n"/>
       <c r="B18" s="167" t="inlineStr">
         <is>
-          <t>romo</t>
+          <t>idalia</t>
         </is>
       </c>
       <c r="C18" s="245" t="n"/>
@@ -42539,7 +42981,7 @@
       <c r="A19" s="33" t="n"/>
       <c r="B19" s="167" t="inlineStr">
         <is>
-          <t>susana</t>
+          <t>viviana</t>
         </is>
       </c>
       <c r="C19" s="245" t="n"/>
@@ -42570,14 +43012,10 @@
     </row>
     <row r="20" ht="46.05" customFormat="1" customHeight="1" s="26">
       <c r="A20" s="33" t="n"/>
-      <c r="B20" s="167" t="inlineStr">
-        <is>
-          <t>pedro</t>
-        </is>
-      </c>
+      <c r="B20" s="167" t="inlineStr"/>
       <c r="C20" s="245" t="n"/>
       <c r="D20" s="71" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E20" s="76">
         <f>($C$5/$D$25)*D20</f>
@@ -42856,14 +43294,14 @@
         <v/>
       </c>
       <c r="E30" s="116" t="n">
-        <v>25600</v>
+        <v>0</v>
       </c>
       <c r="F30" s="115">
         <f>+C8</f>
         <v/>
       </c>
       <c r="G30" s="116" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H30" s="248">
         <f>G41/E41</f>
@@ -42982,24 +43420,40 @@
         <f>D17</f>
         <v/>
       </c>
-      <c r="E33" s="160" t="n"/>
+      <c r="E33" s="160" t="n">
+        <v>0</v>
+      </c>
       <c r="F33" s="256" t="n"/>
-      <c r="G33" s="156" t="n"/>
+      <c r="G33" s="156" t="n">
+        <v>0</v>
+      </c>
       <c r="H33" s="257" t="n"/>
       <c r="I33" s="122">
         <f>IFERROR(G33/E33,"0")</f>
         <v/>
       </c>
-      <c r="J33" s="110" t="n"/>
-      <c r="K33" s="110" t="n"/>
-      <c r="L33" s="110" t="n"/>
-      <c r="M33" s="120" t="n"/>
+      <c r="J33" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="120" t="n">
+        <v>0</v>
+      </c>
       <c r="N33" s="122">
         <f>IFERROR(M33/L33,"0")</f>
         <v/>
       </c>
-      <c r="O33" s="110" t="n"/>
-      <c r="P33" s="111" t="n"/>
+      <c r="O33" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="111" t="n">
+        <v>0</v>
+      </c>
       <c r="Q33" s="37" t="n"/>
     </row>
     <row r="34" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -43013,24 +43467,40 @@
         <f>D18</f>
         <v/>
       </c>
-      <c r="E34" s="147" t="n"/>
+      <c r="E34" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F34" s="260" t="n"/>
-      <c r="G34" s="148" t="n"/>
+      <c r="G34" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H34" s="261" t="n"/>
       <c r="I34" s="122">
         <f>IFERROR(G34/E34,"0")</f>
         <v/>
       </c>
-      <c r="J34" s="113" t="n"/>
-      <c r="K34" s="113" t="n"/>
-      <c r="L34" s="113" t="n"/>
-      <c r="M34" s="121" t="n"/>
+      <c r="J34" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N34" s="122">
         <f>IFERROR(M34/L34,"0")</f>
         <v/>
       </c>
-      <c r="O34" s="113" t="n"/>
-      <c r="P34" s="114" t="n"/>
+      <c r="O34" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q34" s="37" t="n"/>
     </row>
     <row r="35" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -43044,24 +43514,40 @@
         <f>D19</f>
         <v/>
       </c>
-      <c r="E35" s="147" t="n"/>
+      <c r="E35" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F35" s="260" t="n"/>
-      <c r="G35" s="148" t="n"/>
+      <c r="G35" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H35" s="261" t="n"/>
       <c r="I35" s="122">
         <f>IFERROR(G35/E35,"0")</f>
         <v/>
       </c>
-      <c r="J35" s="113" t="n"/>
-      <c r="K35" s="113" t="n"/>
-      <c r="L35" s="113" t="n"/>
-      <c r="M35" s="121" t="n"/>
+      <c r="J35" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N35" s="122">
         <f>IFERROR(M35/L35,"0")</f>
         <v/>
       </c>
-      <c r="O35" s="113" t="n"/>
-      <c r="P35" s="114" t="n"/>
+      <c r="O35" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q35" s="37" t="n"/>
     </row>
     <row r="36" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -43075,24 +43561,40 @@
         <f>D20</f>
         <v/>
       </c>
-      <c r="E36" s="147" t="n"/>
+      <c r="E36" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F36" s="260" t="n"/>
-      <c r="G36" s="148" t="n"/>
+      <c r="G36" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H36" s="261" t="n"/>
       <c r="I36" s="122">
         <f>IFERROR(G36/E36,"0")</f>
         <v/>
       </c>
-      <c r="J36" s="113" t="n"/>
-      <c r="K36" s="113" t="n"/>
-      <c r="L36" s="113" t="n"/>
-      <c r="M36" s="121" t="n"/>
+      <c r="J36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N36" s="122">
         <f>IFERROR(M36/L36,"0")</f>
         <v/>
       </c>
-      <c r="O36" s="113" t="n"/>
-      <c r="P36" s="114" t="n"/>
+      <c r="O36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q36" s="37" t="n"/>
     </row>
     <row r="37" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -43106,24 +43608,40 @@
         <f>D21</f>
         <v/>
       </c>
-      <c r="E37" s="147" t="n"/>
+      <c r="E37" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F37" s="260" t="n"/>
-      <c r="G37" s="148" t="n"/>
+      <c r="G37" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H37" s="261" t="n"/>
       <c r="I37" s="122">
         <f>IFERROR(G37/E37,"0")</f>
         <v/>
       </c>
-      <c r="J37" s="113" t="n"/>
-      <c r="K37" s="113" t="n"/>
-      <c r="L37" s="113" t="n"/>
-      <c r="M37" s="121" t="n"/>
+      <c r="J37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N37" s="122">
         <f>IFERROR(M37/L37,"0")</f>
         <v/>
       </c>
-      <c r="O37" s="113" t="n"/>
-      <c r="P37" s="114" t="n"/>
+      <c r="O37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q37" s="37" t="n"/>
     </row>
     <row r="38" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -43137,24 +43655,40 @@
         <f>D22</f>
         <v/>
       </c>
-      <c r="E38" s="147" t="n"/>
+      <c r="E38" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F38" s="260" t="n"/>
-      <c r="G38" s="148" t="n"/>
+      <c r="G38" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H38" s="261" t="n"/>
       <c r="I38" s="122">
         <f>IFERROR(G38/E38,"0")</f>
         <v/>
       </c>
-      <c r="J38" s="113" t="n"/>
-      <c r="K38" s="113" t="n"/>
-      <c r="L38" s="113" t="n"/>
-      <c r="M38" s="121" t="n"/>
+      <c r="J38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N38" s="122">
         <f>IFERROR(M38/L38,"0")</f>
         <v/>
       </c>
-      <c r="O38" s="113" t="n"/>
-      <c r="P38" s="114" t="n"/>
+      <c r="O38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q38" s="37" t="n"/>
     </row>
     <row r="39" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -43168,24 +43702,40 @@
         <f>D23</f>
         <v/>
       </c>
-      <c r="E39" s="147" t="n"/>
+      <c r="E39" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F39" s="260" t="n"/>
-      <c r="G39" s="148" t="n"/>
+      <c r="G39" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H39" s="261" t="n"/>
       <c r="I39" s="122">
         <f>IFERROR(G39/E39,"0")</f>
         <v/>
       </c>
-      <c r="J39" s="113" t="n"/>
-      <c r="K39" s="113" t="n"/>
-      <c r="L39" s="113" t="n"/>
-      <c r="M39" s="121" t="n"/>
+      <c r="J39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N39" s="122">
         <f>IFERROR(M39/L39,"0")</f>
         <v/>
       </c>
-      <c r="O39" s="113" t="n"/>
-      <c r="P39" s="114" t="n"/>
+      <c r="O39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q39" s="37" t="n"/>
     </row>
     <row r="40" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -43199,24 +43749,40 @@
         <f>D24</f>
         <v/>
       </c>
-      <c r="E40" s="147" t="n"/>
+      <c r="E40" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F40" s="260" t="n"/>
-      <c r="G40" s="148" t="n"/>
+      <c r="G40" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H40" s="261" t="n"/>
       <c r="I40" s="122">
         <f>IFERROR(G40/E40,"0")</f>
         <v/>
       </c>
-      <c r="J40" s="113" t="n"/>
-      <c r="K40" s="113" t="n"/>
-      <c r="L40" s="113" t="n"/>
-      <c r="M40" s="121" t="n"/>
+      <c r="J40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N40" s="122">
         <f>IFERROR(M40/L40,"0")</f>
         <v/>
       </c>
-      <c r="O40" s="113" t="n"/>
-      <c r="P40" s="114" t="n"/>
+      <c r="O40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q40" s="37" t="n"/>
     </row>
     <row r="41" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -44037,7 +44603,7 @@
         </is>
       </c>
       <c r="K1" s="118" t="n">
-        <v>46244.34116924914</v>
+        <v>46248.1869722408</v>
       </c>
       <c r="L1" s="19" t="inlineStr">
         <is>
@@ -44046,7 +44612,7 @@
       </c>
       <c r="M1" s="134" t="inlineStr">
         <is>
-          <t>Interlomas</t>
+          <t>Vallejo</t>
         </is>
       </c>
       <c r="N1" s="118" t="n"/>
@@ -44562,7 +45128,7 @@
       <c r="A18" s="33" t="n"/>
       <c r="B18" s="167" t="inlineStr">
         <is>
-          <t>romo</t>
+          <t>idalia</t>
         </is>
       </c>
       <c r="C18" s="245" t="n"/>
@@ -44595,7 +45161,7 @@
       <c r="A19" s="33" t="n"/>
       <c r="B19" s="167" t="inlineStr">
         <is>
-          <t>susana</t>
+          <t>viviana</t>
         </is>
       </c>
       <c r="C19" s="245" t="n"/>
@@ -44626,14 +45192,10 @@
     </row>
     <row r="20" ht="46.05" customFormat="1" customHeight="1" s="26">
       <c r="A20" s="33" t="n"/>
-      <c r="B20" s="167" t="inlineStr">
-        <is>
-          <t>pedro</t>
-        </is>
-      </c>
+      <c r="B20" s="167" t="inlineStr"/>
       <c r="C20" s="245" t="n"/>
       <c r="D20" s="71" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E20" s="76">
         <f>($C$5/$D$25)*D20</f>
@@ -44912,14 +45474,14 @@
         <v/>
       </c>
       <c r="E30" s="116" t="n">
-        <v>25600</v>
+        <v>0</v>
       </c>
       <c r="F30" s="115">
         <f>+C8</f>
         <v/>
       </c>
       <c r="G30" s="116" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H30" s="248">
         <f>G41/E41</f>
@@ -45038,24 +45600,40 @@
         <f>D17</f>
         <v/>
       </c>
-      <c r="E33" s="160" t="n"/>
+      <c r="E33" s="160" t="n">
+        <v>0</v>
+      </c>
       <c r="F33" s="256" t="n"/>
-      <c r="G33" s="156" t="n"/>
+      <c r="G33" s="156" t="n">
+        <v>0</v>
+      </c>
       <c r="H33" s="257" t="n"/>
       <c r="I33" s="122">
         <f>IFERROR(G33/E33,"0")</f>
         <v/>
       </c>
-      <c r="J33" s="110" t="n"/>
-      <c r="K33" s="110" t="n"/>
-      <c r="L33" s="110" t="n"/>
-      <c r="M33" s="120" t="n"/>
+      <c r="J33" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="120" t="n">
+        <v>0</v>
+      </c>
       <c r="N33" s="122">
         <f>IFERROR(M33/L33,"0")</f>
         <v/>
       </c>
-      <c r="O33" s="110" t="n"/>
-      <c r="P33" s="111" t="n"/>
+      <c r="O33" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="111" t="n">
+        <v>0</v>
+      </c>
       <c r="Q33" s="37" t="n"/>
     </row>
     <row r="34" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -45069,24 +45647,40 @@
         <f>D18</f>
         <v/>
       </c>
-      <c r="E34" s="147" t="n"/>
+      <c r="E34" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F34" s="260" t="n"/>
-      <c r="G34" s="148" t="n"/>
+      <c r="G34" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H34" s="261" t="n"/>
       <c r="I34" s="122">
         <f>IFERROR(G34/E34,"0")</f>
         <v/>
       </c>
-      <c r="J34" s="113" t="n"/>
-      <c r="K34" s="113" t="n"/>
-      <c r="L34" s="113" t="n"/>
-      <c r="M34" s="121" t="n"/>
+      <c r="J34" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N34" s="122">
         <f>IFERROR(M34/L34,"0")</f>
         <v/>
       </c>
-      <c r="O34" s="113" t="n"/>
-      <c r="P34" s="114" t="n"/>
+      <c r="O34" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q34" s="37" t="n"/>
     </row>
     <row r="35" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -45100,24 +45694,40 @@
         <f>D19</f>
         <v/>
       </c>
-      <c r="E35" s="147" t="n"/>
+      <c r="E35" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F35" s="260" t="n"/>
-      <c r="G35" s="148" t="n"/>
+      <c r="G35" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H35" s="261" t="n"/>
       <c r="I35" s="122">
         <f>IFERROR(G35/E35,"0")</f>
         <v/>
       </c>
-      <c r="J35" s="113" t="n"/>
-      <c r="K35" s="113" t="n"/>
-      <c r="L35" s="113" t="n"/>
-      <c r="M35" s="121" t="n"/>
+      <c r="J35" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N35" s="122">
         <f>IFERROR(M35/L35,"0")</f>
         <v/>
       </c>
-      <c r="O35" s="113" t="n"/>
-      <c r="P35" s="114" t="n"/>
+      <c r="O35" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q35" s="37" t="n"/>
     </row>
     <row r="36" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -45131,24 +45741,40 @@
         <f>D20</f>
         <v/>
       </c>
-      <c r="E36" s="147" t="n"/>
+      <c r="E36" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F36" s="260" t="n"/>
-      <c r="G36" s="148" t="n"/>
+      <c r="G36" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H36" s="261" t="n"/>
       <c r="I36" s="122">
         <f>IFERROR(G36/E36,"0")</f>
         <v/>
       </c>
-      <c r="J36" s="113" t="n"/>
-      <c r="K36" s="113" t="n"/>
-      <c r="L36" s="113" t="n"/>
-      <c r="M36" s="121" t="n"/>
+      <c r="J36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N36" s="122">
         <f>IFERROR(M36/L36,"0")</f>
         <v/>
       </c>
-      <c r="O36" s="113" t="n"/>
-      <c r="P36" s="114" t="n"/>
+      <c r="O36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q36" s="37" t="n"/>
     </row>
     <row r="37" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -45162,24 +45788,40 @@
         <f>D21</f>
         <v/>
       </c>
-      <c r="E37" s="147" t="n"/>
+      <c r="E37" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F37" s="260" t="n"/>
-      <c r="G37" s="148" t="n"/>
+      <c r="G37" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H37" s="261" t="n"/>
       <c r="I37" s="122">
         <f>IFERROR(G37/E37,"0")</f>
         <v/>
       </c>
-      <c r="J37" s="113" t="n"/>
-      <c r="K37" s="113" t="n"/>
-      <c r="L37" s="113" t="n"/>
-      <c r="M37" s="121" t="n"/>
+      <c r="J37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N37" s="122">
         <f>IFERROR(M37/L37,"0")</f>
         <v/>
       </c>
-      <c r="O37" s="113" t="n"/>
-      <c r="P37" s="114" t="n"/>
+      <c r="O37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q37" s="37" t="n"/>
     </row>
     <row r="38" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -45193,24 +45835,40 @@
         <f>D22</f>
         <v/>
       </c>
-      <c r="E38" s="147" t="n"/>
+      <c r="E38" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F38" s="260" t="n"/>
-      <c r="G38" s="148" t="n"/>
+      <c r="G38" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H38" s="261" t="n"/>
       <c r="I38" s="122">
         <f>IFERROR(G38/E38,"0")</f>
         <v/>
       </c>
-      <c r="J38" s="113" t="n"/>
-      <c r="K38" s="113" t="n"/>
-      <c r="L38" s="113" t="n"/>
-      <c r="M38" s="121" t="n"/>
+      <c r="J38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N38" s="122">
         <f>IFERROR(M38/L38,"0")</f>
         <v/>
       </c>
-      <c r="O38" s="113" t="n"/>
-      <c r="P38" s="114" t="n"/>
+      <c r="O38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q38" s="37" t="n"/>
     </row>
     <row r="39" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -45224,24 +45882,40 @@
         <f>D23</f>
         <v/>
       </c>
-      <c r="E39" s="147" t="n"/>
+      <c r="E39" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F39" s="260" t="n"/>
-      <c r="G39" s="148" t="n"/>
+      <c r="G39" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H39" s="261" t="n"/>
       <c r="I39" s="122">
         <f>IFERROR(G39/E39,"0")</f>
         <v/>
       </c>
-      <c r="J39" s="113" t="n"/>
-      <c r="K39" s="113" t="n"/>
-      <c r="L39" s="113" t="n"/>
-      <c r="M39" s="121" t="n"/>
+      <c r="J39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N39" s="122">
         <f>IFERROR(M39/L39,"0")</f>
         <v/>
       </c>
-      <c r="O39" s="113" t="n"/>
-      <c r="P39" s="114" t="n"/>
+      <c r="O39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q39" s="37" t="n"/>
     </row>
     <row r="40" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -45255,24 +45929,40 @@
         <f>D24</f>
         <v/>
       </c>
-      <c r="E40" s="147" t="n"/>
+      <c r="E40" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F40" s="260" t="n"/>
-      <c r="G40" s="148" t="n"/>
+      <c r="G40" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H40" s="261" t="n"/>
       <c r="I40" s="122">
         <f>IFERROR(G40/E40,"0")</f>
         <v/>
       </c>
-      <c r="J40" s="113" t="n"/>
-      <c r="K40" s="113" t="n"/>
-      <c r="L40" s="113" t="n"/>
-      <c r="M40" s="121" t="n"/>
+      <c r="J40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N40" s="122">
         <f>IFERROR(M40/L40,"0")</f>
         <v/>
       </c>
-      <c r="O40" s="113" t="n"/>
-      <c r="P40" s="114" t="n"/>
+      <c r="O40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q40" s="37" t="n"/>
     </row>
     <row r="41" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -46093,7 +46783,7 @@
         </is>
       </c>
       <c r="K1" s="118" t="n">
-        <v>46244.34116924914</v>
+        <v>46248.18697224295</v>
       </c>
       <c r="L1" s="19" t="inlineStr">
         <is>
@@ -46102,7 +46792,7 @@
       </c>
       <c r="M1" s="134" t="inlineStr">
         <is>
-          <t>Interlomas</t>
+          <t>Vallejo</t>
         </is>
       </c>
       <c r="N1" s="118" t="n"/>
@@ -46616,7 +47306,7 @@
       <c r="A18" s="33" t="n"/>
       <c r="B18" s="167" t="inlineStr">
         <is>
-          <t>romo</t>
+          <t>idalia</t>
         </is>
       </c>
       <c r="C18" s="245" t="n"/>
@@ -46649,7 +47339,7 @@
       <c r="A19" s="33" t="n"/>
       <c r="B19" s="167" t="inlineStr">
         <is>
-          <t>susana</t>
+          <t>viviana</t>
         </is>
       </c>
       <c r="C19" s="245" t="n"/>
@@ -46680,14 +47370,10 @@
     </row>
     <row r="20" ht="46.05" customFormat="1" customHeight="1" s="26">
       <c r="A20" s="33" t="n"/>
-      <c r="B20" s="167" t="inlineStr">
-        <is>
-          <t>pedro</t>
-        </is>
-      </c>
+      <c r="B20" s="167" t="inlineStr"/>
       <c r="C20" s="245" t="n"/>
       <c r="D20" s="71" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E20" s="76">
         <f>($C$5/$D$25)*D20</f>
@@ -46966,14 +47652,14 @@
         <v/>
       </c>
       <c r="E30" s="116" t="n">
-        <v>25600</v>
+        <v>0</v>
       </c>
       <c r="F30" s="115">
         <f>+C8</f>
         <v/>
       </c>
       <c r="G30" s="116" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H30" s="248">
         <f>G41/E41</f>
@@ -47092,24 +47778,40 @@
         <f>D17</f>
         <v/>
       </c>
-      <c r="E33" s="160" t="n"/>
+      <c r="E33" s="160" t="n">
+        <v>0</v>
+      </c>
       <c r="F33" s="256" t="n"/>
-      <c r="G33" s="156" t="n"/>
+      <c r="G33" s="156" t="n">
+        <v>0</v>
+      </c>
       <c r="H33" s="257" t="n"/>
       <c r="I33" s="122">
         <f>IFERROR(G33/E33,"0")</f>
         <v/>
       </c>
-      <c r="J33" s="110" t="n"/>
-      <c r="K33" s="110" t="n"/>
-      <c r="L33" s="110" t="n"/>
-      <c r="M33" s="120" t="n"/>
+      <c r="J33" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="120" t="n">
+        <v>0</v>
+      </c>
       <c r="N33" s="122">
         <f>IFERROR(M33/L33,"0")</f>
         <v/>
       </c>
-      <c r="O33" s="110" t="n"/>
-      <c r="P33" s="111" t="n"/>
+      <c r="O33" s="110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="111" t="n">
+        <v>0</v>
+      </c>
       <c r="Q33" s="37" t="n"/>
     </row>
     <row r="34" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -47123,24 +47825,40 @@
         <f>D18</f>
         <v/>
       </c>
-      <c r="E34" s="147" t="n"/>
+      <c r="E34" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F34" s="260" t="n"/>
-      <c r="G34" s="148" t="n"/>
+      <c r="G34" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H34" s="261" t="n"/>
       <c r="I34" s="122">
         <f>IFERROR(G34/E34,"0")</f>
         <v/>
       </c>
-      <c r="J34" s="113" t="n"/>
-      <c r="K34" s="113" t="n"/>
-      <c r="L34" s="113" t="n"/>
-      <c r="M34" s="121" t="n"/>
+      <c r="J34" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N34" s="122">
         <f>IFERROR(M34/L34,"0")</f>
         <v/>
       </c>
-      <c r="O34" s="113" t="n"/>
-      <c r="P34" s="114" t="n"/>
+      <c r="O34" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q34" s="37" t="n"/>
     </row>
     <row r="35" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -47154,24 +47872,40 @@
         <f>D19</f>
         <v/>
       </c>
-      <c r="E35" s="147" t="n"/>
+      <c r="E35" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F35" s="260" t="n"/>
-      <c r="G35" s="148" t="n"/>
+      <c r="G35" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H35" s="261" t="n"/>
       <c r="I35" s="122">
         <f>IFERROR(G35/E35,"0")</f>
         <v/>
       </c>
-      <c r="J35" s="113" t="n"/>
-      <c r="K35" s="113" t="n"/>
-      <c r="L35" s="113" t="n"/>
-      <c r="M35" s="121" t="n"/>
+      <c r="J35" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N35" s="122">
         <f>IFERROR(M35/L35,"0")</f>
         <v/>
       </c>
-      <c r="O35" s="113" t="n"/>
-      <c r="P35" s="114" t="n"/>
+      <c r="O35" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q35" s="37" t="n"/>
     </row>
     <row r="36" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -47185,24 +47919,40 @@
         <f>D20</f>
         <v/>
       </c>
-      <c r="E36" s="147" t="n"/>
+      <c r="E36" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F36" s="260" t="n"/>
-      <c r="G36" s="148" t="n"/>
+      <c r="G36" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H36" s="261" t="n"/>
       <c r="I36" s="122">
         <f>IFERROR(G36/E36,"0")</f>
         <v/>
       </c>
-      <c r="J36" s="113" t="n"/>
-      <c r="K36" s="113" t="n"/>
-      <c r="L36" s="113" t="n"/>
-      <c r="M36" s="121" t="n"/>
+      <c r="J36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N36" s="122">
         <f>IFERROR(M36/L36,"0")</f>
         <v/>
       </c>
-      <c r="O36" s="113" t="n"/>
-      <c r="P36" s="114" t="n"/>
+      <c r="O36" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q36" s="37" t="n"/>
     </row>
     <row r="37" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -47216,24 +47966,40 @@
         <f>D21</f>
         <v/>
       </c>
-      <c r="E37" s="147" t="n"/>
+      <c r="E37" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F37" s="260" t="n"/>
-      <c r="G37" s="148" t="n"/>
+      <c r="G37" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H37" s="261" t="n"/>
       <c r="I37" s="122">
         <f>IFERROR(G37/E37,"0")</f>
         <v/>
       </c>
-      <c r="J37" s="113" t="n"/>
-      <c r="K37" s="113" t="n"/>
-      <c r="L37" s="113" t="n"/>
-      <c r="M37" s="121" t="n"/>
+      <c r="J37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N37" s="122">
         <f>IFERROR(M37/L37,"0")</f>
         <v/>
       </c>
-      <c r="O37" s="113" t="n"/>
-      <c r="P37" s="114" t="n"/>
+      <c r="O37" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q37" s="37" t="n"/>
     </row>
     <row r="38" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -47247,24 +48013,40 @@
         <f>D22</f>
         <v/>
       </c>
-      <c r="E38" s="147" t="n"/>
+      <c r="E38" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F38" s="260" t="n"/>
-      <c r="G38" s="148" t="n"/>
+      <c r="G38" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H38" s="261" t="n"/>
       <c r="I38" s="122">
         <f>IFERROR(G38/E38,"0")</f>
         <v/>
       </c>
-      <c r="J38" s="113" t="n"/>
-      <c r="K38" s="113" t="n"/>
-      <c r="L38" s="113" t="n"/>
-      <c r="M38" s="121" t="n"/>
+      <c r="J38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N38" s="122">
         <f>IFERROR(M38/L38,"0")</f>
         <v/>
       </c>
-      <c r="O38" s="113" t="n"/>
-      <c r="P38" s="114" t="n"/>
+      <c r="O38" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q38" s="37" t="n"/>
     </row>
     <row r="39" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -47278,24 +48060,40 @@
         <f>D23</f>
         <v/>
       </c>
-      <c r="E39" s="147" t="n"/>
+      <c r="E39" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F39" s="260" t="n"/>
-      <c r="G39" s="148" t="n"/>
+      <c r="G39" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H39" s="261" t="n"/>
       <c r="I39" s="122">
         <f>IFERROR(G39/E39,"0")</f>
         <v/>
       </c>
-      <c r="J39" s="113" t="n"/>
-      <c r="K39" s="113" t="n"/>
-      <c r="L39" s="113" t="n"/>
-      <c r="M39" s="121" t="n"/>
+      <c r="J39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N39" s="122">
         <f>IFERROR(M39/L39,"0")</f>
         <v/>
       </c>
-      <c r="O39" s="113" t="n"/>
-      <c r="P39" s="114" t="n"/>
+      <c r="O39" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q39" s="37" t="n"/>
     </row>
     <row r="40" ht="46.05" customFormat="1" customHeight="1" s="26">
@@ -47309,24 +48107,40 @@
         <f>D24</f>
         <v/>
       </c>
-      <c r="E40" s="147" t="n"/>
+      <c r="E40" s="147" t="n">
+        <v>0</v>
+      </c>
       <c r="F40" s="260" t="n"/>
-      <c r="G40" s="148" t="n"/>
+      <c r="G40" s="148" t="n">
+        <v>0</v>
+      </c>
       <c r="H40" s="261" t="n"/>
       <c r="I40" s="122">
         <f>IFERROR(G40/E40,"0")</f>
         <v/>
       </c>
-      <c r="J40" s="113" t="n"/>
-      <c r="K40" s="113" t="n"/>
-      <c r="L40" s="113" t="n"/>
-      <c r="M40" s="121" t="n"/>
+      <c r="J40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="N40" s="122">
         <f>IFERROR(M40/L40,"0")</f>
         <v/>
       </c>
-      <c r="O40" s="113" t="n"/>
-      <c r="P40" s="114" t="n"/>
+      <c r="O40" s="113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="114" t="n">
+        <v>0</v>
+      </c>
       <c r="Q40" s="37" t="n"/>
     </row>
     <row r="41" ht="46.05" customFormat="1" customHeight="1" s="26">
